--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45949</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45055</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46080</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46037</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46227</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45566</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45916</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46098</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45649</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>46261</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45985</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46041</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46255</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>46252</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46119</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46032</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46038</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46121</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46258</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44668</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44549</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>44841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44476</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44778</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>44732</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>44887</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45236</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45579</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45057</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45681</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45681</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45447</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45404</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45092</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45326</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>45295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44634</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44662</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45222</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45219</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45414</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45693</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45601</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45769</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45572</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45326</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45027</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45672</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45285</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45680</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45751</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45733</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45566</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45348</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45749</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45670</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45188</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44669</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>46051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44823</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>46031</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45643</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>46140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45313</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>46069</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45369</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45912</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44785</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>46044</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>46083</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44671</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45681</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45924</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44887</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45644</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45938</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45941</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45941</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45273</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>46149</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45427</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45594</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45961</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45964</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45574</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45972</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45194</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45979</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45414</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45309</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44509</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45651</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45919</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45311</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44527</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45425</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44811</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45566</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45166</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45995</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45964</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45764</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>46010</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>46167</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>46014</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45538</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>46019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>46024</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46024</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45295</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>46024</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>46024</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>46024</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46024</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>46027</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45027</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45608</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>46031</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>46030</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>46174</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>46032</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>46032</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>45453</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>46174</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>46042</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>46042</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45572</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>46048</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46048</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>46048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45578</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>46050</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>46055</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>46168</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44512</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45525</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>46182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45660</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>46010</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45022</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45534</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45534</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45664</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46029</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>46009</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45419</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45961</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46038</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44585</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44519</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45509</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46076</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45560</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46080</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>46185</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45435</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45224</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45467</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44601</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45886</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46195</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45651</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>46106</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>46105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>45219</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45503</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>44494</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45370</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46121</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>46125</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45664</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45260</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>46048</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>46139</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45912</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>44868</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45695</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46248</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45148</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45174</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45077</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46253</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45478</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46259</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>46259</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>46259</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45048</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>46259</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>46259</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45404</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>46262</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46107</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45572</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45769</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45713</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45566</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45566</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45776</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>46248</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45461</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>46272</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45475</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45709</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45495</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>46233</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45565</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45785</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45453</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45694</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45348</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45735</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45826</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45826</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45845</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45848</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44627</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45345</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44315</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45341</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44510</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45377</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44649</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44963</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>44963</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>46088</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46181</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45949</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45055</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46227</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45916</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45572</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45649</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46098</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45566</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>46261</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45985</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>46045</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46041</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>45275</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45846</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46255</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46032</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46038</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46121</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45764</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44841</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45572</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45467</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45414</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44823</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46014</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>46019</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46024</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>46024</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46024</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>46024</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45348</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46024</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>46024</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>46030</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>46031</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46032</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>46032</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>46034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45531</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45414</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>46042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46050</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45904</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>46055</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44585</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45534</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45664</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46038</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45022</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45961</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46029</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45924</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45566</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45572</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45651</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44671</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45566</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>46080</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45938</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45693</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45941</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45941</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45769</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44662</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>46105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>46107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44895</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45295</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45348</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45961</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44494</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45027</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>46121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45601</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>46125</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45972</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45972</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45735</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45435</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>46083</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>46048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45546</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45912</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45749</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45037</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46010</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46051</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45660</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45964</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45695</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45643</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46140</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44785</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>46139</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45826</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45751</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45681</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45912</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45681</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45174</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>46048</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45313</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45692</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45572</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46149</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46154</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45651</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45579</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45919</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45845</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45848</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46168</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>46045</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45608</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44627</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45478</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45425</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46174</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45326</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45447</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>46168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45574</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45566</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45345</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44527</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46185</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45404</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45085</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>44509</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45370</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46195</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45670</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45148</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45275</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45427</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45572</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45027</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44669</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>46253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45166</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46259</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46259</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46259</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>46259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45764</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46262</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45194</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45219</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45713</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45309</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45769</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>46272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45258</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45285</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45326</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45733</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45594</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45219</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>46233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45560</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>46248</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>46286</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44512</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46289</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44601</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45236</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45057</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45311</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45453</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45525</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45608</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44887</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45295</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44634</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45538</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45369</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44897</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45219</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45148</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45077</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45680</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44747</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45244</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45776</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45461</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45475</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45495</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45453</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45785</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45694</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>44315</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45341</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44510</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45377</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44935</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44649</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44963</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44963</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>46088</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>46181</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45949</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45055</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46227</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45916</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>45572</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45649</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46098</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45566</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>46261</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45985</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>46045</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46041</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>45275</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45846</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46255</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>45608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46032</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46038</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46121</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45726</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45764</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>46240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44841</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>44811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45572</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45467</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45414</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44823</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>46014</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>46019</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46024</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>46024</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46024</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>46024</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45348</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>46024</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>46024</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>46030</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>46031</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46032</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>46032</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>46034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45531</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45414</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>46042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46050</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45904</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>46055</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45188</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44585</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45534</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45664</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46038</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45022</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45961</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46029</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45924</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45566</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45572</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46076</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45651</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44671</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45566</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>46080</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45938</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45693</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45941</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45941</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45769</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44662</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>46105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>46106</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>46107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44895</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45295</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45348</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45961</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44494</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45027</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>46121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45601</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>46125</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45972</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45972</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45735</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45435</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>46083</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>46048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45546</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45912</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45749</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45037</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46010</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46051</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45660</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45964</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45695</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45643</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46140</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44785</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>46139</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45826</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45751</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45681</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45912</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45681</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45174</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>46048</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45313</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45692</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45572</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46149</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46154</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45651</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45579</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45919</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45845</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45848</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46168</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>46045</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45608</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44627</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45478</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45425</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46174</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45326</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45447</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>46168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45574</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45566</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45345</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44527</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46185</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45404</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45085</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>44509</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45370</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46195</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45670</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45148</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45275</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45427</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45572</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45027</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44669</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>46253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45166</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46259</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46259</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46259</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>46259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45764</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46262</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45194</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45219</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45713</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45260</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45309</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45769</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>46272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45258</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45285</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45326</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45733</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45594</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45219</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>46233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45560</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>46248</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>46286</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44512</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46289</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44601</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45236</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45057</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45311</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45453</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45525</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45608</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44887</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45295</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44634</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45538</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45369</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44897</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45219</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45148</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45077</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45680</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44747</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45244</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45776</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45461</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45475</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45495</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45453</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45785</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45694</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>44315</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45341</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44510</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45377</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44935</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44649</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44963</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44963</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>46088</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>46181</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45949</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45055</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45916</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46098</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45566</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45478</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>46045</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>46112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46041</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45588</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>46032</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>46038</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>46121</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>46119</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45764</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>46258</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46240</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45593</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44841</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45236</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45579</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45681</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45681</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45404</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45545</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44747</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45453</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45326</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45295</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44634</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45113</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46010</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45222</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>46024</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46024</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>46024</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>46024</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>46024</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>46024</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>46027</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>46031</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>46031</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>46030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>46032</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>46032</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45904</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45219</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45414</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>46042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45348</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>46048</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46048</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46050</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45693</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45601</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46055</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45326</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46010</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45022</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45534</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45534</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45664</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>46009</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45961</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>46038</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44585</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44519</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45938</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45938</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45941</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45941</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45027</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>46076</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45957</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45174</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45961</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45735</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45285</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45751</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45680</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45972</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45886</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46106</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46105</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45566</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45348</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45219</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45992</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46121</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>46125</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45826</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45670</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45670</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45995</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45188</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44669</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46139</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44823</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>44973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45546</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45533</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45848</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45369</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44671</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>46051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44887</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44627</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46031</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45643</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>46140</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45313</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45692</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45912</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44785</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46083</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45681</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45427</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46149</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45345</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45594</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45651</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45919</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45194</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45258</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46168</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45414</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46045</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46174</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45260</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44509</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46174</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46168</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45311</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44527</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45425</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44811</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45166</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45275</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45531</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45764</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46195</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45538</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45295</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45027</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45608</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45453</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>46259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46259</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45572</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46259</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>46259</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45578</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44512</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46262</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45525</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45085</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45660</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45419</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45509</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45560</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45435</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45224</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45467</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44601</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45651</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45219</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45503</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46289</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45370</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45664</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46293</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46286</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45260</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46248</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45244</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>44868</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46297</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45695</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45931</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45148</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45077</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45478</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45404</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45572</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45572</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45572</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45769</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45566</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45566</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45776</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45461</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45475</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45709</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45495</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45097</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45565</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44315</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45341</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44510</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45377</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44935</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>44649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44963</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46088</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46181</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45949</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45055</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45916</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46098</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45566</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45478</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>46045</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>46112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46041</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>46098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45588</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>46032</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>46038</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>46121</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44511</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45846</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>46119</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45764</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>46258</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46240</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45593</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44841</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45236</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45579</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45681</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45681</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45404</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45545</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44747</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45453</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45694</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45326</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45295</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44634</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45113</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46010</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45222</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>46024</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46024</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>46024</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>46024</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>46024</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>46024</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>46027</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>46031</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>46031</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>46030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>46032</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>46032</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45904</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45219</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45414</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>46042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45348</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>46048</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46048</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46050</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45693</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45601</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>46055</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45326</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46010</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45022</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45534</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45534</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45664</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>46009</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45961</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>46038</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44585</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44519</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45938</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45938</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45941</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45941</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45027</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>46076</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45946</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45952</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45957</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45174</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45961</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45735</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45285</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45751</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45680</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45972</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45886</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46106</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>46105</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45566</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45348</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45219</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45992</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46121</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>46125</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45826</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45670</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45670</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45995</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45188</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45608</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44669</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46139</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44823</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>44973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45546</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45533</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45848</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45369</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44671</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>46051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44887</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44627</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46031</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45643</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>46140</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45313</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45692</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45912</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44785</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46083</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45681</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45427</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46149</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45345</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45594</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45651</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45919</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45194</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45258</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46168</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45414</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46045</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46174</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45260</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44509</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46174</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46168</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45311</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44527</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45425</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44811</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45166</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45275</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45531</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45764</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46195</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45538</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45295</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45027</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45608</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45453</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>46259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>46259</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45572</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46259</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>46259</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45578</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44512</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46262</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45525</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45085</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45660</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45419</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45509</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45560</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45435</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45224</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46233</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45467</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44601</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45651</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45219</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45503</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46289</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45370</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45664</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46293</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46286</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45260</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46248</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45244</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>44868</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46297</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45695</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45931</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45148</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45174</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45077</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45478</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45404</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45572</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45572</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45572</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45769</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45566</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45566</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45776</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45461</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45475</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45709</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45495</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45097</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45565</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44315</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45341</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44510</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45377</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44935</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>44649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44963</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46088</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46181</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45055</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45949</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45916</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45572</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45649</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45566</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45985</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>46112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>46041</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>46098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>46121</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>46032</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>45846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46038</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>46119</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>46240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>44778</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44698</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45419</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45453</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45525</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44811</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>45295</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>45467</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45664</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>45538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45414</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45369</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44823</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45509</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45608</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45478</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45425</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45148</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45326</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45077</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45680</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44747</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45447</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45531</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>45244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45414</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45904</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45776</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45574</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45566</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>44527</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45709</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45475</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45495</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45404</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45435</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45453</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45694</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45370</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45566</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44973</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45574</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45572</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45651</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45670</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45670</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45148</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45348</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45566</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45275</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45174</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45693</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45427</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45572</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45222</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45027</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45938</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45937</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44662</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45608</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45938</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44669</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45941</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45941</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45295</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45735</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45348</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45608</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44494</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45027</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45166</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>45826</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45601</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45826</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45957</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45961</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>45764</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45435</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45194</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45219</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45845</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45972</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45713</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45848</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45972</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45260</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44627</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45309</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45769</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45285</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45345</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45113</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45224</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45660</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45695</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45326</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45273</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45733</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45886</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45219</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45681</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45681</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45503</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>46107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45572</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45404</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45560</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46121</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>46125</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44512</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46010</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45964</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46014</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>46019</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>46083</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46048</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46024</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>46024</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>46024</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46024</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46024</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>46024</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45912</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45749</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>46031</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46032</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46032</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46031</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>44601</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46031</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45533</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>46042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>46051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>46069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45643</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46140</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45236</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>44785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>46048</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45311</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45681</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>46050</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>46055</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45313</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45692</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46009</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44585</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44519</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45534</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45534</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46010</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45664</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45022</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45961</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46029</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46076</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46154</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46080</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45651</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45919</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46167</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>46168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46045</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>46182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46195</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>46107</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>46233</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46248</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46293</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>46248</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>46297</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45931</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46259</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46259</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>46259</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46259</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46262</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45964</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45055</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45949</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>46037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46080</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45202</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45916</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45572</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45649</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45566</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45985</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>46112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>46041</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46045</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>46098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44511</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>46121</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>46032</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>45846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>46044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46038</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>46119</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>46240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>44511</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>44668</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44549</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>44778</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44698</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45419</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45453</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45525</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44811</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>45295</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>45467</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45664</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>45538</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45414</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45369</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44823</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45509</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45608</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45478</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45425</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45148</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45326</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45077</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45680</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44747</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45447</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45531</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>45244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45414</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45904</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45904</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45776</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45574</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45566</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>44527</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45709</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45475</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45495</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45404</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45435</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45453</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45694</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45370</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45566</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44973</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45574</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45572</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45651</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45670</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45670</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45148</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45348</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>45566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45566</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45275</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45174</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45693</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45427</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45572</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45222</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45027</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45938</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45937</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44662</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45608</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45938</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44669</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45941</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45941</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45295</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45735</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45348</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45608</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44494</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45027</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45166</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>45826</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45601</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45826</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45957</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45961</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45219</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>45764</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45435</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45194</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45219</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45845</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45972</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45713</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45848</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45972</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45260</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44627</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45309</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45769</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>45285</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45345</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45113</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45224</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45660</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45695</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45326</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45273</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45733</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45886</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45219</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45681</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45681</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45503</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>46107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45572</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45404</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45560</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46121</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>46125</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44512</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46010</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45964</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46014</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>46019</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>46083</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46048</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>46024</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>46024</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>46024</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46024</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46024</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>46024</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45912</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45749</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>46031</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46032</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46032</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46031</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>44601</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46031</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45533</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>46042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>46051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>46069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45643</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46140</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45236</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>44785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>46048</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45311</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45681</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>46050</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>46055</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45313</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45692</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>46009</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44585</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44519</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45534</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45534</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46010</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45664</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45022</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45961</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46029</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46076</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46154</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46080</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45651</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45919</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46167</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>46168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>46045</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>46182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46195</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>46107</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>46233</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>46289</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46248</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46293</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>46248</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>46297</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45931</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46259</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46259</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>46259</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46259</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46262</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45964</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>46310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45949</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46080</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46037</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46310</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45202</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46227</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45566</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45478</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45916</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>46098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45985</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45275</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46041</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>46098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46119</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>46032</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>46038</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>46121</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44668</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44549</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45236</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45579</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45681</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45681</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45404</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45326</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44662</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45222</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45414</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45693</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45601</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45572</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45326</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45027</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45285</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45751</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45733</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45566</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45348</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45670</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45670</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>46051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45188</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>46031</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>45643</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>46048</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45912</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>46044</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>46083</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44669</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45681</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44823</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44973</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>45369</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>46149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>45931</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45931</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45938</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45937</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45941</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45941</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>46154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45957</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45961</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45273</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45427</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45972</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45972</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45594</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45574</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46168</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46167</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45194</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>46045</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45995</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45258</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45414</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45309</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44509</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>46010</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>46014</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45311</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44527</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45425</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46019</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44811</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>46024</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46024</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>46024</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>46024</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45566</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>46031</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45166</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45275</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>46032</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>46032</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45531</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>46042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>46182</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>46048</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>46048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>46048</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>46050</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>46055</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45764</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45538</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46010</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45022</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45534</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45534</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>46009</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45961</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>46038</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44585</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44519</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45295</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>46076</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45027</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45608</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46080</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45453</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45572</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45886</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45578</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45174</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46106</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44512</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>46107</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45525</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45660</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45419</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>46121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>46125</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45509</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45560</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45435</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45224</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>46048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45912</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45467</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44601</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45651</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45503</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44494</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45370</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46272</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45664</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45148</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>46233</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44868</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45695</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45478</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>46289</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46248</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45048</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46293</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>46286</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45572</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45572</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45572</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46297</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45769</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45713</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45566</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45566</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45776</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45461</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45709</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46185</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45495</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45565</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46259</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45785</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>46259</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45453</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45694</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>46259</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>46259</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>46259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46027</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45348</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>46262</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45735</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45826</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45848</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44627</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45345</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>44169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>46310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45949</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46080</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>46037</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46310</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45202</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46227</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45566</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45478</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45916</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>46098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45985</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45275</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46041</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>46098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>46255</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45846</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46119</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>46032</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>46038</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>46121</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45726</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44668</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44549</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45236</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45579</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45681</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45681</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45057</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45404</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44747</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45326</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44662</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45222</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45414</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45693</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45601</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45572</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45326</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45027</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>45174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45285</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45751</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45733</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45566</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45348</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45670</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45670</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>46051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45188</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>46031</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>45643</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>46048</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>46140</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45912</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44785</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>46044</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>46083</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44669</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45681</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44823</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44973</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>45369</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>46149</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>45931</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45931</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45938</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45937</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45941</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45941</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>46154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45957</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45961</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45273</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45427</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45972</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45972</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45594</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45574</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46168</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46167</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45194</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>46045</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45995</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45258</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45414</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45309</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44509</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>46010</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>46014</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45311</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44527</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45425</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46019</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44811</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>46024</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>46024</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>46024</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>46024</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45566</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>46031</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45166</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45275</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>46032</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>46032</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45531</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>46042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>46182</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>46048</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>46048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>46048</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>46050</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>46055</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45764</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45538</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46010</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45022</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45534</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45534</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>46009</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45961</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>46038</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44585</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>44519</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45295</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>46076</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45027</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45608</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46080</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45453</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45572</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45886</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45578</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45174</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46106</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44512</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>46107</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45525</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45085</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45660</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45419</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>46121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>46125</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45509</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45560</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45435</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45224</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>46048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45912</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45467</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44601</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45651</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45503</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44494</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45370</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46272</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45664</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45148</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45260</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>46233</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44868</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45695</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45478</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>46289</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46248</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45048</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46293</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>46286</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45404</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45572</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45572</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45572</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46297</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45769</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45713</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45566</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45566</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45776</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45461</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45709</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46185</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45495</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45565</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46259</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45785</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>46259</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45453</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45694</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>46259</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>46259</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>46259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46027</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45348</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>46262</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45735</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45826</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45848</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44627</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45345</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>46310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>44169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>46310</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46080</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46037</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45916</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46098</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45572</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45566</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45478</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>46045</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>46255</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>46041</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45588</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45275</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>46119</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>46195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46195</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46032</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46240</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>46044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>46038</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>46258</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>46121</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>46153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44668</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44549</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44811</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45572</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45467</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45414</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45919</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>46167</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45419</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45931</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45236</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45057</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45937</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45311</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45941</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45941</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>46168</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44868</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45453</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>45525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>46182</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45952</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45295</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45578</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45664</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45961</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45538</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>46195</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45369</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>45972</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45219</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45148</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44747</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44823</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>46107</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45509</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45776</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45461</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45037</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45709</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45475</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45565</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45495</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45964</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45964</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46233</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>45453</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>46014</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>46019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>46024</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>46024</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>46024</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45785</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>46024</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46024</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45694</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>46032</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46032</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46031</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>46034</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45348</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46050</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>46286</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46055</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>46248</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>46293</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46248</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45735</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44585</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45534</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45534</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46010</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45022</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45961</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>46076</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>46080</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>46297</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>46185</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45931</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45886</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45845</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>46259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45848</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>46105</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46106</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>46259</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44627</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46121</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45414</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46125</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46262</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45545</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45188</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46083</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45435</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>46048</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45566</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44973</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46272</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46051</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>46069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>46140</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46044</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44671</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44785</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45566</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46031</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45912</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45681</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>46048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45313</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45692</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45693</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45769</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>46149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44662</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45295</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45348</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45651</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45608</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44494</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45027</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45601</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45435</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45113</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45224</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45660</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45695</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45273</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45751</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45681</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45174</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45572</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45579</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45608</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45478</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45425</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45326</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45447</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45574</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45566</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>44527</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45404</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45085</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44509</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45670</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45148</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45275</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45427</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45027</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44669</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45219</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45764</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45194</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45219</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45309</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45769</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45260</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45258</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45285</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45326</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45594</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45219</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45503</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45404</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45560</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt GAGNEF.xlsx
+++ b/Översikt GAGNEF.xlsx
@@ -601,7 +601,7 @@
         <v>45951</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>46127</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>46310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>44169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>46310</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46080</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46037</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45916</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46098</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45572</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45566</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45478</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>46045</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>46255</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>46041</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45588</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45275</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>46119</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>46195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46195</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46032</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46240</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>46044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>46038</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>46258</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>46121</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44511</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>46153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44691</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44668</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44549</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44841</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44778</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>44887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44811</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45572</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45467</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45414</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45919</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>46167</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45419</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45931</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45236</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45057</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45937</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45311</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45941</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45941</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>46168</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44868</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45453</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>45525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>46182</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45952</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45295</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45578</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45664</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45961</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45538</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>46195</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45369</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>45972</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45219</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45148</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45077</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44747</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44823</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>46107</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45509</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45776</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45461</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45037</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45709</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45475</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45565</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45495</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45964</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>46010</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45964</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46233</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>45453</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>46014</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>46019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>46024</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>46024</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>46024</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45785</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>46024</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46024</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45694</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>46032</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46032</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46031</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46031</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>46034</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45348</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>46048</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46050</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>46286</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46055</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>46248</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>46293</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46248</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45735</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44585</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45534</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45534</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46010</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45022</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45961</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>46029</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>46076</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>46080</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>46297</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>46185</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45931</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45886</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45845</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>46259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45848</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>46105</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46106</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>46259</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44627</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46121</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45414</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46125</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46262</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>46027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45545</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45188</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46083</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45435</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>46048</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45566</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44973</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46272</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46051</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>46069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>46140</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46044</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44671</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44785</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45566</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46031</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45912</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45681</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>46048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45313</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45692</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45693</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45769</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>46149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44662</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45295</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45348</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45651</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45608</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44494</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45027</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45601</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45435</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45113</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45224</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45660</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45695</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45273</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45751</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45681</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45174</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45572</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45579</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45608</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45478</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45425</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45326</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45447</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45574</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45566</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>44527</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45404</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45085</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44509</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45670</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45148</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45275</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45427</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45027</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44669</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45219</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45764</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45194</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45219</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45309</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45769</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45260</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45258</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45285</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45326</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45594</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45219</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45503</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45404</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45560</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45377</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44649</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>44963</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>46088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>46181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
